--- a/docs/extratimethesis.xlsx
+++ b/docs/extratimethesis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Dropbox\pc\Documents\masterthesis\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91C19567-3F5C-4112-93AD-8510F24404BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1120B3C-4D86-4B87-95C8-CE04E6587D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F89B3D90-2AD4-430A-B434-1ECC6F5A4820}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F89B3D90-2AD4-430A-B434-1ECC6F5A4820}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="8">
   <si>
     <t>September</t>
   </si>
@@ -59,7 +59,10 @@
     <t>hw design + simulations</t>
   </si>
   <si>
-    <t>thesis writing</t>
+    <t>November</t>
+  </si>
+  <si>
+    <t>Thesis writing</t>
   </si>
 </sst>
 </file>
@@ -431,30 +434,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF2CC7D-9858-4BAC-8E42-9B6D9E956412}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.90625" customWidth="1"/>
     <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -462,10 +472,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -473,10 +486,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -484,10 +500,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -495,10 +514,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -506,10 +528,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -517,10 +542,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -528,10 +556,13 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -539,10 +570,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -550,10 +584,13 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -561,10 +598,13 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -572,10 +612,13 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -583,10 +626,13 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -594,10 +640,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -605,135 +654,216 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
